--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0004.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0004.xlsx
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Shop</t>
+          <t>Cửa hàng</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Trở về</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Apply</t>
+          <t>Áp dụng</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Đăng Ký Lunite</t>
+          <t>Lunite Subscription</t>
         </is>
       </c>
     </row>
@@ -15069,7 +15069,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Đăng Ký Lunite</t>
+          <t>Lunite Subscription</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Chạm để nhận thưởng Đăng Ký Lunite hôm nay</t>
+          <t>Chạm để nhận thưởng Lunite Subscription hôm nay</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Tạm dừng</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
     </row>
@@ -19361,7 +19361,7 @@
       <c r="M291" t="inlineStr">
         <is>
           <t>Nhận tất cả phần thưởng Insider Channel
-Increase Cấp Podcast lên 10</t>
+Tăng Cấp Podcast lên 10</t>
         </is>
       </c>
     </row>
@@ -21051,7 +21051,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Refresh</t>
+          <t>Làm mới</t>
         </is>
       </c>
     </row>
@@ -21181,7 +21181,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
     </row>
@@ -23001,7 +23001,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Đã sở hữu</t>
         </is>
       </c>
     </row>
@@ -26186,7 +26186,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
     </row>
@@ -27096,7 +27096,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Tìm kiếm</t>
         </is>
       </c>
     </row>
@@ -27421,7 +27421,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
     </row>
@@ -27811,7 +27811,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
     </row>
@@ -30346,7 +30346,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Send</t>
+          <t>Gửi</t>
         </is>
       </c>
     </row>
@@ -30671,7 +30671,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Chuyện Kể Từ Núi Firmament</t>
+          <t>Chuyện Kể Từ Mt. Firmament</t>
         </is>
       </c>
     </row>
